--- a/Users List V0.1 (03.03.2026).xlsx
+++ b/Users List V0.1 (03.03.2026).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harms\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harms\Desktop\CH_FILES\Development\dms_demo_tau5\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DA1917-61A8-46F1-843F-C442EC8A1A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F62E8D3-D743-4788-9DCD-71F67A29A42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,21 @@
     <sheet name="Users" sheetId="1" r:id="rId1"/>
     <sheet name="#Ref" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -719,9 +730,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="4" width="28.28515625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="10" width="28.28515625" style="5" customWidth="1"/>
+    <col min="2" max="10" width="28.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="53.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -51489,7 +51498,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E1048576" xr:uid="{E0714E57-9219-4D78-9664-22ED1742F60B}">
-      <formula1>$B5:$B500</formula1>
+      <formula1>$B$5:$B$500</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
